--- a/data/trans_orig/IP11D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Provincia-trans_orig.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121450</t>
+          <t>122166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119145</t>
+          <t>119215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126575</t>
+          <t>126673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244050</t>
+          <t>244137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252824</t>
+          <t>252761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54216</t>
+          <t>55253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>60822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66447</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>117809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124652</t>
+          <t>124586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>41753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45564</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55798</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90420</t>
+          <t>90743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101013</t>
+          <t>100959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118727</t>
+          <t>118743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>123927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150789</t>
+          <t>150667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272451</t>
+          <t>272771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278845</t>
+          <t>278822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,47 +3524,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>9123</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>24445</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>24495</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>654846</t>
+          <t>654836</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>662819</t>
+          <t>662467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>742766</t>
+          <t>743236</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>756143</t>
+          <t>756256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1401508</t>
+          <t>1401558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1416947</t>
+          <t>1416880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP11D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,64 +833,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56481</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79366</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7963</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4529</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8381</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112587</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107872</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>114936</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>125580</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>122166</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>99256</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>96021</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100550</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>124115</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>119215</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>126673</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>291</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>249695</t>
+          <t>211843</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244137</t>
+          <t>206008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252761</t>
+          <t>214630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5417</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6341</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57410</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53960</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58741</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>57553</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55253</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>55862</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52695</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64852</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60822</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66466</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>194</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117809</t>
+          <t>109876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124586</t>
+          <t>115287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1862,64 +1862,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78134</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2205,64 +2205,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4414</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9698</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46386</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>39908</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48425</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>81,54%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44854</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>41753</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>44541</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>41916</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>45766</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>53141</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>46488</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>55808</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>167</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>97996</t>
+          <t>90927</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90743</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100959</t>
+          <t>93571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5765</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>139546</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>135926</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>140409</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>122401</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>118743</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>123927</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>154237</t>
+          <t>120290</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150667</t>
+          <t>116463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>121918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>276638</t>
+          <t>259836</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272771</t>
+          <t>255641</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278822</t>
+          <t>262143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140409</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140409</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140409</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279595</t>
+          <t>262938</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279595</t>
+          <t>262938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279595</t>
+          <t>262938</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3234,64 +3234,64 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>131235</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>140148</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>156795</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>288030</t>
+          <t>299569</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131235</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131235</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131235</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140148</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140148</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140148</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288030</t>
+          <t>299569</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288030</t>
+          <t>299569</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288030</t>
+          <t>299569</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10120</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,17 +3539,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>691235</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>683789</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>695476</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>659562</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>654836</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>751360</t>
+          <t>623030</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>743236</t>
+          <t>617765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>756256</t>
+          <t>626065</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1410923</t>
+          <t>1314265</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1401558</t>
+          <t>1305083</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1416880</t>
+          <t>1319314</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
